--- a/documentação/Testes/Caso de Teste/UC19 - DISPONIBILIZAR CONSULTAS .xlsx
+++ b/documentação/Testes/Caso de Teste/UC19 - DISPONIBILIZAR CONSULTAS .xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="88">
   <si>
     <t xml:space="preserve">Caso de Teste</t>
   </si>
@@ -63,7 +63,13 @@
 - Dias da Semana (checkboxes).</t>
   </si>
   <si>
-    <t xml:space="preserve">(Valida pré-condição)</t>
+    <t xml:space="preserve">Resultado correto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mensagem pedindo autorização da administração.</t>
   </si>
   <si>
     <t xml:space="preserve">CT02 - Acesso ao Formulário (Sem clínicas vinculadas)</t>
@@ -120,6 +126,9 @@
     <t xml:space="preserve">Sistema destaca campos em vermelho com mensagem: "Preencha todos os campos obrigatórios."</t>
   </si>
   <si>
+    <t xml:space="preserve">Mensagem exibida é uma mensagem padrão de campo: “ Preencha esse campo.”</t>
+  </si>
+  <si>
     <t xml:space="preserve">CT05 - Período Inválido (Data Fim &lt; Data Início)</t>
   </si>
   <si>
@@ -135,7 +144,16 @@
     <t xml:space="preserve">Sistema exibe: "Data final deve ser posterior à data inicial."</t>
   </si>
   <si>
+    <t xml:space="preserve">Resultado errado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOK</t>
+  </si>
+  <si>
     <t xml:space="preserve">(Valida FA3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sistema salva da mesma forma, mesmo com dados incorretos.</t>
   </si>
   <si>
     <t xml:space="preserve">CT06 - Horário Inválido (Horário Fim ≤ Horário Início)</t>
@@ -204,6 +222,9 @@
   </si>
   <si>
     <t xml:space="preserve">(Valida RN01 e FA1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sistema salva com horários já ocupados.</t>
   </si>
   <si>
     <t xml:space="preserve">CT10 - Voltar sem Salvar</t>
@@ -311,7 +332,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -365,6 +386,18 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="15"/>
       <color rgb="FF404040"/>
       <name val="Arial"/>
@@ -414,44 +447,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -527,15 +580,121 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="32.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="37.33"/>
@@ -568,7 +727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -581,263 +740,370 @@
       <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="51.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="G3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="146.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>22</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="51.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="9" customFormat="false" ht="51.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="8"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
